--- a/excel-files/PASIG/NAGPAYONG HIGH SCHOOL.xlsx
+++ b/excel-files/PASIG/NAGPAYONG HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{119D7821-B8A4-4B8C-BD11-DF3A8621FB21}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0655D58-0B90-4AA0-94FF-2F1E2B7E4A1D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3664,7 +3664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3764,12 +3764,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="19.5" hidden="1" customHeight="1">
+    <row r="7" spans="1:8" ht="19.5" customHeight="1">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.5" hidden="1" customHeight="1">
+    <row r="12" spans="1:8" ht="19.5" customHeight="1">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3869,12 +3869,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="19.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.5" hidden="1" customHeight="1">
+    <row r="19" spans="1:8" ht="19.5" customHeight="1">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="19.5" hidden="1" customHeight="1">
+    <row r="20" spans="1:8" ht="19.5" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -4004,7 +4004,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="38.25" hidden="1" customHeight="1">
+    <row r="23" spans="1:8" ht="38.25" customHeight="1">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4194,7 +4194,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4384,7 +4384,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -9562,8 +9562,8 @@
     <protectedRange sqref="C124:C150" name="Textbooks_2"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 F91:F122 R91:R122 L91:L122 X91:X122 L124:L150 R124:R150 F124:F150 X124:X150" xr:uid="{1E841372-844C-48F7-A0CD-EBBF3436C3A1}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F91:F122 R91:R122 L91:L122 L124:L150 R124:R150 X91:X122 X124:X150 F124:F150" xr:uid="{1E841372-844C-48F7-A0CD-EBBF3436C3A1}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 S124:S150 M124:M150 Y124:Y150 G124:G150" xr:uid="{3F7B9B36-E418-4119-845D-A7CDAA91A4D5}">
@@ -9571,6 +9571,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M91:M122 Y91:Y122 S91:S122 G91:G122" xr:uid="{B95D4ACB-7131-4FD8-BEAD-B28C0A31BBCB}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E124:E150 E91:E122 E81:E89 E71:E79 E61:E69 E51:E59 L56 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{058D07C4-D803-40DA-A35D-F087ACA720A9}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9728,7 +9731,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" hidden="1" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
         <v>110</v>
       </c>
@@ -9807,7 +9810,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -9876,7 +9879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -9945,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -10014,7 +10017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -10083,7 +10086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -10152,7 +10155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -10221,7 +10224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -10290,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -10359,7 +10362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -10372,7 +10375,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -10441,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -10510,7 +10513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -10579,7 +10582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -10648,7 +10651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -10717,7 +10720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -10786,7 +10789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -10855,7 +10858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -10924,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -10938,7 +10941,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -11007,7 +11010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -11076,7 +11079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -11145,7 +11148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -11214,7 +11217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -11283,7 +11286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -11352,7 +11355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -11421,7 +11424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -11490,7 +11493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -11559,7 +11562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -11573,7 +11576,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -11642,7 +11645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -11711,7 +11714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -11780,7 +11783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -11849,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -11918,7 +11921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -11987,7 +11990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -12056,7 +12059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -12125,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -12194,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -12208,7 +12211,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -12277,7 +12280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -12346,7 +12349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -12415,7 +12418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -12484,7 +12487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -12553,7 +12556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -12622,7 +12625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -12691,7 +12694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -12760,7 +12763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -12829,7 +12832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -12843,7 +12846,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -12912,7 +12915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -12981,7 +12984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -13050,7 +13053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -13119,7 +13122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -13188,7 +13191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -13257,7 +13260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -13326,7 +13329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -13395,7 +13398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -13464,7 +13467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -21414,15 +21417,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S136:S181 M136:M181 Y136:Y181 G136:G181" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F134 R103:R134 L103:L134 X103:X134 L136:L181 R136:R181 F136:F181 X136:X181" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X163:X181 R163:R181 F163:F181 L163:L181" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M134 Y14:Y134 S4:S134 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G134" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D89 F136:F162 F103:F134 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L136:L162 L103:L134 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R136:R162 R103:R134 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X136:X162 X103:X134 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{110B16F3-FB37-42EF-BB42-8FC56A78F3AD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21583,7 +21589,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25" hidden="1">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -21652,7 +21658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5" hidden="1">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -21721,7 +21727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5" hidden="1">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -21790,7 +21796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5" hidden="1">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -21859,7 +21865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5" hidden="1">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -21928,7 +21934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5" hidden="1">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -21997,7 +22003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5" hidden="1">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -22066,7 +22072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5" hidden="1">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -22135,8 +22141,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="12" spans="1:27" ht="38.25" hidden="1">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -22205,7 +22211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5" hidden="1">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -22274,7 +22280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5" hidden="1">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -22343,7 +22349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5" hidden="1">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -22412,7 +22418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5" hidden="1">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -22481,7 +22487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5" hidden="1">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -22550,7 +22556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5" hidden="1">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -22619,7 +22625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5" hidden="1">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -22688,8 +22694,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="21" spans="1:27" ht="38.25" hidden="1">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -22758,7 +22764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5" hidden="1">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -22827,7 +22833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5" hidden="1">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -22896,7 +22902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5" hidden="1">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -22965,7 +22971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5" hidden="1">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -23034,7 +23040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5" hidden="1">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -23103,7 +23109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5" hidden="1">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -23172,7 +23178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5" hidden="1">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -23241,7 +23247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5" hidden="1">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -23310,8 +23316,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="31" spans="1:27" ht="19.5" hidden="1">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -23380,7 +23386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5" hidden="1">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -23449,7 +23455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5" hidden="1">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -23518,7 +23524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5" hidden="1">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -23587,7 +23593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25" hidden="1">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -23656,7 +23662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5" hidden="1">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -23725,7 +23731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5" hidden="1">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -23794,7 +23800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5" hidden="1">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -23863,7 +23869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5" hidden="1">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -23932,7 +23938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5" hidden="1">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -24001,7 +24007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5" hidden="1">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -24070,8 +24076,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="43" spans="1:27" ht="19.5" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -24140,7 +24146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5" hidden="1">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -24209,7 +24215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5" hidden="1">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -24278,7 +24284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5" hidden="1">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -24347,7 +24353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25" hidden="1">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -24416,7 +24422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5" hidden="1">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -24485,7 +24491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5" hidden="1">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -24554,7 +24560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5" hidden="1">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -24623,7 +24629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5" hidden="1">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -24692,7 +24698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5" hidden="1">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -24761,7 +24767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5" hidden="1">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -24830,8 +24836,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="55" spans="1:27" ht="19.5" hidden="1">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -24900,7 +24906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5" hidden="1">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -24969,7 +24975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5" hidden="1">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -25038,7 +25044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5" hidden="1">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -25107,7 +25113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25" hidden="1">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -25176,7 +25182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5" hidden="1">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -25245,7 +25251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5" hidden="1">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -25314,7 +25320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5" hidden="1">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -25383,7 +25389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5" hidden="1">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -25452,7 +25458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5" hidden="1">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -25521,7 +25527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5" hidden="1">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -33031,8 +33037,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y102:Y112 S102:S112 M102:M112 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M66:M76 G66:G76 Y66:Y76 S66:S76 S78:S88 M78:M88 G78:G88 Y78:Y88 Y90:Y100 S90:S100 M90:M100 G90:G100 G102:G112 M114:M145 Y114:Y145 S114:S145 G114:G145" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X66:X76 X78:X88 X55:X65 X90:X100 X102:X112 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L66:L76 L78:L88 L55:L65 L90:L100 L102:L112 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R66:R76 R78:R88 R55:R65 R90:R100 R102:R112 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 X147:X173 F78:F88 F55:F65 F3:F10 F90:F100 F102:F112 F12:F19 F114:F145 R114:R145 L114:L145 X114:X145 L147:L173 R147:R173 F147:F173 F66:F76" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F147:F173 F114:F145 F102:F112 F90:F100 F78:F88 F55:F76 F43:F52 F31:F41 F21:F29 F12:F19 F3:F10 L147:L173 L114:L145 L102:L112 L90:L100 L78:L88 L55:L76 L43:L52 L31:L41 L21:L29 L12:L19 L3:L10 R147:R173 R114:R145 R102:R112 R90:R100 R78:R88 R55:R76 R43:R52 R31:R41 R21:R29 R12:R19 R3:R10 X147:X173 X114:X145 X102:X112 X90:X100 X78:X88 X55:X76 X43:X52 X31:X41 X21:X29 X12:X19 X3:X10 L53 R53 X53 F53" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S147:S173 M147:M173 Y147:Y173 G147:G173" xr:uid="{92810BB6-F517-408D-95CA-B44BE055EBD3}">
       <formula1>"CO,RO,SDO"</formula1>
